--- a/Results/TestCases/XLSX/login_TestCases.xlsx
+++ b/Results/TestCases/XLSX/login_TestCases.xlsx
@@ -72,7 +72,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>SKIPPED</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>TC_LOGIN_02</t>
@@ -249,7 +249,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF5A6268"/>
+      <color rgb="FF107C41"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
@@ -268,7 +268,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
+        <fgColor rgb="FFD1E7DD"/>
       </patternFill>
     </fill>
   </fills>

--- a/Results/TestCases/XLSX/login_TestCases.xlsx
+++ b/Results/TestCases/XLSX/login_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="109">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,15 +58,14 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The OrangeHRM login page is loaded in the browser.</t>
+  </si>
+  <si>
+    <t>1. Enter the username and password, then click the Login button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- It should be loaded
+- The header text should equal 'Dashboard'</t>
   </si>
   <si>
     <t>High</t>
@@ -84,6 +83,9 @@
     <t>Negative</t>
   </si>
   <si>
+    <t>- The error text should equal 'Invalid credentials'</t>
+  </si>
+  <si>
     <t>TC_LOGIN_03</t>
   </si>
   <si>
@@ -96,6 +98,12 @@
     <t>Verify password field masks the input characters</t>
   </si>
   <si>
+    <t>1. Perform the actions described in the test title</t>
+  </si>
+  <si>
+    <t>- The password type should equal 'password'</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -105,28 +113,50 @@
     <t>Verify login page UI elements are visible</t>
   </si>
   <si>
+    <t xml:space="preserve">- The brand logo should be visible
+- The Login title should display the text 'Login'
+- The 'Forgot your password?' link should be visible
+- The Username field should be visible
+- The Password field should be visible
+- The Login button should be visible
+- The copyright footer text should be visible</t>
+  </si>
+  <si>
     <t>TC_LOGIN_06</t>
   </si>
   <si>
     <t>Verify credential hint box displays default credentials</t>
   </si>
   <si>
+    <t xml:space="preserve">- The hint text should contain 'Admin'
+- The hint text should contain 'admin123'</t>
+  </si>
+  <si>
     <t>TC_LOGIN_07</t>
   </si>
   <si>
     <t>Verify login page title contains OrangeHRM</t>
   </si>
   <si>
+    <t>- The title should contain 'OrangeHRM'</t>
+  </si>
+  <si>
     <t>TC_LOGIN_08</t>
   </si>
   <si>
     <t>Verify login page URL contains auth/login</t>
   </si>
   <si>
+    <t>- The page.url() should contain '/auth/login'</t>
+  </si>
+  <si>
     <t>TC_LOGIN_09</t>
   </si>
   <si>
-    <t>Verify input placeholders display correct text</t>
+    <t>Verify input placeholders display non-empty hint text</t>
+  </si>
+  <si>
+    <t>- The length should be greater than '0'</t>
   </si>
   <si>
     <t>TC_LOGIN_10</t>
@@ -135,101 +165,200 @@
     <t>Verify username field is focused on page load</t>
   </si>
   <si>
+    <t>- The Username field should receive keyboard focus</t>
+  </si>
+  <si>
     <t>TC_LOGIN_11</t>
   </si>
   <si>
     <t>Verify tab key navigation flows logically from username to password</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Focus the Username field
+2. Press the 'Tab' key</t>
+  </si>
+  <si>
+    <t>- The Password field should receive keyboard focus</t>
+  </si>
+  <si>
     <t>TC_LOGIN_12</t>
   </si>
   <si>
     <t>Verify login button is enabled by default</t>
   </si>
   <si>
+    <t>- The Login button should be enabled</t>
+  </si>
+  <si>
     <t>TC_LOGIN_13</t>
   </si>
   <si>
     <t>Verify brand logo has descriptive alt text</t>
   </si>
   <si>
+    <t>- The alt text should equal 'company-branding'</t>
+  </si>
+  <si>
     <t>TC_LOGIN_14</t>
   </si>
   <si>
     <t>Verify brand logo height and width attributes are positive</t>
   </si>
   <si>
+    <t xml:space="preserve">- The bounding box should not be null
+- The width should be greater than '0'
+- The height should be greater than '0'</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
     <t>TC_LOGIN_15</t>
   </si>
   <si>
     <t>Verify copyright footer contains correct organization name</t>
   </si>
   <si>
+    <t>- The text should contain 'OrangeHRM'</t>
+  </si>
+  <si>
     <t>TC_LOGIN_16</t>
   </si>
   <si>
     <t>Verify input fields are empty on default page load</t>
   </si>
   <si>
+    <t xml:space="preserve">- The Username field should have the value ''
+- The Password field should have the value ''</t>
+  </si>
+  <si>
     <t>TC_LOGIN_17</t>
   </si>
   <si>
     <t>Verify custom CSS properties on Username label</t>
   </si>
   <si>
+    <t>- The 'Username' element should not be null</t>
+  </si>
+  <si>
     <t>TC_LOGIN_18</t>
   </si>
   <si>
     <t>Verify login page layout is responsive under mobile width</t>
   </si>
   <si>
+    <t>1. Resize the browser viewport to simulate a mobile device</t>
+  </si>
+  <si>
+    <t>- The is visible should be present</t>
+  </si>
+  <si>
     <t>TC_LOGIN_19</t>
   </si>
   <si>
     <t>Verify autocomplete tags are present on input fields</t>
   </si>
   <si>
+    <t>- The autocomplete === null || autocomplete === 'off' should equal 'true'</t>
+  </si>
+  <si>
     <t>TC_LOGIN_20</t>
   </si>
   <si>
     <t>Verify error panel CSS classes contain validation properties</t>
   </si>
   <si>
+    <t>- It should have class</t>
+  </si>
+  <si>
     <t>TC_LOGIN_21</t>
   </si>
   <si>
     <t>Verify login card is visible</t>
   </si>
   <si>
+    <t>- The card should be visible</t>
+  </si>
+  <si>
     <t>TC_LOGIN_22</t>
   </si>
   <si>
     <t>Verify credential hint box contains header title</t>
   </si>
   <si>
+    <t>- The title should display the text 'Login'</t>
+  </si>
+  <si>
     <t>TC_LOGIN_23</t>
   </si>
   <si>
     <t>Verify forgot password link has pointer cursor on hover</t>
   </si>
   <si>
+    <t>- The cursor should equal 'pointer'</t>
+  </si>
+  <si>
     <t>TC_LOGIN_24</t>
   </si>
   <si>
     <t>Verify HTML tag has lang attribute set to en</t>
   </si>
   <si>
+    <t>- The lang === null || lang === 'en' should equal 'true'</t>
+  </si>
+  <si>
     <t>TC_LOGIN_25</t>
   </si>
   <si>
     <t>Verify connection security protocol is HTTPS</t>
+  </si>
+  <si>
+    <t>- The url.starts with('https://') should equal 'true'</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_26</t>
+  </si>
+  <si>
+    <t>Verify successful login persists session across page reload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Reload the current page</t>
+  </si>
+  <si>
+    <t>- The header text should equal 'Dashboard'</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_27</t>
+  </si>
+  <si>
+    <t>Verify login fails with a numeric-only username</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_28</t>
+  </si>
+  <si>
+    <t>Verify pressing Enter with username filled but password empty triggers required validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 'Admin' into the Username field
+2. Press the 'Enter' key while focused on the Password field</t>
+  </si>
+  <si>
+    <t>- The password error should equal 'Required'</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_29</t>
+  </si>
+  <si>
+    <t>Verify login page handles an extremely long password input without crashing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -253,8 +382,14 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFA51D24"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,6 +404,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1E7DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -310,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -319,6 +459,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -660,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -769,7 +912,7 @@
         <v>16</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -780,7 +923,7 @@
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -789,13 +932,13 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -804,7 +947,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -815,7 +958,7 @@
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -824,25 +967,25 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
@@ -850,34 +993,34 @@
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -885,7 +1028,7 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -894,25 +1037,25 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -920,7 +1063,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -929,25 +1072,25 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -955,7 +1098,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -964,25 +1107,25 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>19</v>
@@ -990,7 +1133,7 @@
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -999,25 +1142,25 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>19</v>
@@ -1025,7 +1168,7 @@
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1034,25 +1177,25 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>19</v>
@@ -1060,7 +1203,7 @@
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1069,25 +1212,25 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>19</v>
@@ -1095,7 +1238,7 @@
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1104,25 +1247,25 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1130,7 +1273,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1139,25 +1282,25 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>19</v>
@@ -1165,7 +1308,7 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1174,33 +1317,33 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1209,25 +1352,25 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>19</v>
@@ -1235,7 +1378,7 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1244,25 +1387,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>19</v>
@@ -1270,7 +1413,7 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1279,25 +1422,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>19</v>
@@ -1305,7 +1448,7 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1314,25 +1457,25 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>19</v>
@@ -1340,7 +1483,7 @@
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1349,25 +1492,25 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>19</v>
@@ -1375,7 +1518,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1384,13 +1527,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1399,10 +1542,10 @@
         <v>16</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>19</v>
@@ -1410,7 +1553,7 @@
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1419,25 +1562,25 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>19</v>
@@ -1445,7 +1588,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1454,25 +1597,25 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1480,7 +1623,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1489,25 +1632,25 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1515,7 +1658,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1524,25 +1667,25 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1550,7 +1693,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1559,27 +1702,167 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="3" t="s">
+      <c r="I28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>19</v>
       </c>
     </row>

--- a/Results/TestCases/XLSX/login_TestCases.xlsx
+++ b/Results/TestCases/XLSX/login_TestCases.xlsx
@@ -199,6 +199,9 @@
     <t>- The alt text should equal 'company-branding'</t>
   </si>
   <si>
+    <t>FAILED</t>
+  </si>
+  <si>
     <t>TC_LOGIN_14</t>
   </si>
   <si>
@@ -208,9 +211,6 @@
     <t xml:space="preserve">- The bounding box should not be null
 - The width should be greater than '0'
 - The height should be greater than '0'</t>
-  </si>
-  <si>
-    <t>FAILED</t>
   </si>
   <si>
     <t>TC_LOGIN_15</t>
@@ -1302,13 +1302,13 @@
       <c r="J14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>19</v>
+      <c r="K14" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1317,13 +1317,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1332,13 +1332,13 @@
         <v>28</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1372,8 +1372,8 @@
       <c r="J16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>19</v>
+      <c r="K16" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1407,8 +1407,8 @@
       <c r="J17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>19</v>
+      <c r="K17" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
